--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Fecha:</t>
   </si>
   <si>
+    <t>01/05/2025</t>
+  </si>
+  <si>
     <t>Nombre:</t>
   </si>
   <si>
@@ -95,7 +98,7 @@
     <t>CN-02D1TJ-CH600-396-00T7-A01</t>
   </si>
   <si>
-    <t>srtiugkjhghoñlk.</t>
+    <t>Entrega de equipo de cómputo</t>
   </si>
   <si>
     <t>Teclado</t>
@@ -138,6 +141,9 @@
   </si>
   <si>
     <t>CNK5WW3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00179</t>
   </si>
   <si>
     <t>Monitor</t>
@@ -311,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
@@ -453,6 +459,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="true">
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -848,8 +858,8 @@
       <c r="H8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="9">
-        <v>45770.0</v>
+      <c r="I8" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="15">
@@ -865,11 +875,11 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="15">
       <c r="A10" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -892,23 +902,23 @@
     <row r="12" spans="1:10" customHeight="1" ht="15">
       <c r="A12" s="2"/>
       <c r="B12" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="18"/>
     </row>
@@ -925,7 +935,7 @@
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="15">
       <c r="A14" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -971,217 +981,217 @@
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="15">
       <c r="A18" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="22"/>
       <c r="H18" s="22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="15">
-      <c r="A19" s="22">
+      <c r="A19" s="38">
         <v>1</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="22" t="s">
+      <c r="B19" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="C19" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22" t="s">
+      <c r="D19" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22" t="s">
+      <c r="E19" s="38"/>
+      <c r="F19" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="22"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="22">
+      <c r="A20" s="38">
         <v>2</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="22" t="s">
+      <c r="B20" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="C20" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22" t="s">
+      <c r="D20" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="22">
+      <c r="A21" s="38">
         <v>3</v>
       </c>
-      <c r="B21" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="22" t="s">
+      <c r="B21" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22" t="s">
+      <c r="C21" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="22">
+      <c r="A22" s="38">
         <v>4</v>
       </c>
-      <c r="B22" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="22" t="s">
+      <c r="B22" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="C22" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22" t="s">
+      <c r="D22" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="22">
+      <c r="A23" s="38">
         <v>5</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="22" t="s">
+      <c r="B23" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22" t="s">
+      <c r="C23" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="22">
-        <v>6</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>22</v>
-      </c>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
       <c r="D24" s="22" t="s">
         <v>41</v>
       </c>
       <c r="E24" s="22"/>
-      <c r="F24" s="22" t="s">
-        <v>42</v>
-      </c>
+      <c r="F24" s="22"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
+      <c r="A25" s="38">
+        <v>6</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
+      <c r="A29" s="27"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
@@ -1194,7 +1204,7 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1205,171 +1215,173 @@
       <c r="H31" s="28"/>
       <c r="I31" s="28"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A32" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="27">
-      <c r="A33" s="28" t="s">
+    <row r="32" spans="1:10" customHeight="1" ht="15">
+      <c r="A32" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="39">
-      <c r="A35" s="31" t="s">
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A33" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="27">
+      <c r="A34" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="15">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="39">
+      <c r="A36" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="2"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="33"/>
       <c r="I37" s="33"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="32"/>
-      <c r="B38" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="36" t="s">
+      <c r="A39" s="32"/>
+      <c r="B39" s="34" t="s">
         <v>52</v>
       </c>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="G39" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="2"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="36" t="s">
+        <v>54</v>
+      </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="34" t="str">
-        <f>C10</f>
-        <v>Oswaldo Salmeron Almeida</v>
-      </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
       <c r="B43" s="34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="34" t="str">
+        <f>C10</f>
+        <v>Oswaldo Salmeron Almeida</v>
+      </c>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="34" t="str">
         <f>C12</f>
         <v>Analista de TI</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
@@ -1378,20 +1390,31 @@
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="32"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="15">
+      <c r="A47" s="32"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1410,23 +1433,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G39:I39"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="G43:I43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G44:I44"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1445,11 +1468,14 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H19:I24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H19:I25"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Fecha:</t>
   </si>
   <si>
+    <t>28/04/2025</t>
+  </si>
+  <si>
     <t>Nombre:</t>
   </si>
   <si>
@@ -95,9 +98,6 @@
     <t>CN-02D1TJ-CH600-396-00T7-A01</t>
   </si>
   <si>
-    <t>srtiugkjhghoñlk.</t>
-  </si>
-  <si>
     <t>Teclado</t>
   </si>
   <si>
@@ -129,24 +129,6 @@
   </si>
   <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Inspiron 15 3000</t>
-  </si>
-  <si>
-    <t>CNK5WW3</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>E2724HS</t>
-  </si>
-  <si>
-    <t>3DX6G04</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -311,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
@@ -453,6 +435,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="true">
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -848,8 +834,8 @@
       <c r="H8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="9">
-        <v>45770.0</v>
+      <c r="I8" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="15">
@@ -865,11 +851,11 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="15">
       <c r="A10" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -892,23 +878,23 @@
     <row r="12" spans="1:10" customHeight="1" ht="15">
       <c r="A12" s="2"/>
       <c r="B12" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="18"/>
     </row>
@@ -925,7 +911,7 @@
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="15">
       <c r="A14" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -971,204 +957,186 @@
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="15">
       <c r="A18" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="22"/>
       <c r="H18" s="22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="15">
-      <c r="A19" s="22">
+      <c r="A19" s="38">
         <v>1</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="22" t="s">
+      <c r="B19" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="C19" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22" t="s">
+      <c r="D19" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22" t="s">
+      <c r="E19" s="38"/>
+      <c r="F19" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="22"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="22">
+      <c r="A20" s="38">
         <v>2</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22" t="s">
+      <c r="E20" s="38"/>
+      <c r="F20" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="22">
+      <c r="A21" s="38">
         <v>3</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22" t="s">
+      <c r="E21" s="38"/>
+      <c r="F21" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="22">
+      <c r="A22" s="38">
         <v>4</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22" t="s">
+      <c r="E22" s="38"/>
+      <c r="F22" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="22">
-        <v>5</v>
-      </c>
-      <c r="B23" s="22" t="s">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+    </row>
+    <row r="24" spans="1:10" customHeight="1" ht="15">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+    </row>
+    <row r="25" spans="1:10" customHeight="1" ht="15">
+      <c r="A25" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="22" t="s">
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+    </row>
+    <row r="26" spans="1:10" customHeight="1" ht="15">
+      <c r="A26" s="27"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+    </row>
+    <row r="27" spans="1:10" customHeight="1" ht="15">
+      <c r="A27" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22" t="s">
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+    </row>
+    <row r="28" spans="1:10" customHeight="1" ht="15">
+      <c r="A28" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-    </row>
-    <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="22">
-        <v>6</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-    </row>
-    <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-    </row>
-    <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-    </row>
-    <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-    </row>
-    <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
@@ -1179,22 +1147,23 @@
       <c r="H29" s="28"/>
       <c r="I29" s="28"/>
     </row>
-    <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-    </row>
-    <row r="31" spans="1:10" customHeight="1" ht="15">
+    <row r="30" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A30" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" customHeight="1" ht="27">
       <c r="A31" s="28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1205,101 +1174,96 @@
       <c r="H31" s="28"/>
       <c r="I31" s="28"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A32" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="27">
-      <c r="A33" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
+    <row r="32" spans="1:10" customHeight="1" ht="15">
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="39">
+      <c r="A33" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="39">
-      <c r="A35" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="15">
+      <c r="A35" s="2"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
+      <c r="B36" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
+      <c r="G36" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="2"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="36" t="s">
+        <v>46</v>
+      </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="32"/>
-      <c r="B38" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="37"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="36" t="s">
-        <v>52</v>
-      </c>
+      <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -1308,90 +1272,68 @@
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="2"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
+      <c r="B40" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
+      <c r="G40" s="34" t="str">
+        <f>C10</f>
+        <v>Oswaldo Salmeron Almeida</v>
+      </c>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="B41" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="G41" s="34" t="str">
+        <f>C12</f>
+        <v>Analista de TI</v>
+      </c>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="34" t="str">
-        <f>C10</f>
-        <v>Oswaldo Salmeron Almeida</v>
-      </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="34" t="str">
-        <f>C12</f>
-        <v>Analista de TI</v>
-      </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="A44" s="32"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-    </row>
-    <row r="45" spans="1:10" customHeight="1" ht="15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="32"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1410,23 +1352,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="G41:I41"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1439,17 +1381,11 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="H22:I22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H19:I24"/>
+    <mergeCell ref="H19:I22"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>28/04/2025</t>
+    <t>05/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -86,12 +86,27 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Inspiron 15 3000</t>
+  </si>
+  <si>
+    <t>CNK5WW3</t>
+  </si>
+  <si>
+    <t>Se entrega equipo de computo</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00179</t>
+  </si>
+  <si>
     <t>Cargador Laptop</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
     <t>HA65NS5-00</t>
   </si>
   <si>
@@ -129,6 +144,15 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>E2724HS</t>
+  </si>
+  <si>
+    <t>3DX6G04</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -996,46 +1020,40 @@
         <v>25</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
+      <c r="H19" s="38" t="s">
+        <v>26</v>
+      </c>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="38">
-        <v>2</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
       <c r="A21" s="38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1043,127 +1061,150 @@
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
       <c r="A22" s="38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="38" t="s">
         <v>33</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>35</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
       <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
+      <c r="A23" s="38">
+        <v>4</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
+      <c r="A24" s="38">
+        <v>5</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
+      <c r="A25" s="38">
+        <v>6</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
+      <c r="A28" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-    </row>
-    <row r="30" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A30" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" customHeight="1" ht="27">
+      <c r="A29" s="27"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+    </row>
+    <row r="30" spans="1:10" customHeight="1" ht="15">
+      <c r="A30" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+    </row>
+    <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1175,132 +1216,129 @@
       <c r="I31" s="28"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="39">
-      <c r="A33" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
+      <c r="A32" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A33" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="27">
+      <c r="A34" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="2"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="32"/>
-      <c r="B36" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="39">
+      <c r="A36" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="36" t="s">
-        <v>46</v>
-      </c>
+      <c r="A37" s="32"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="2"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="G39" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="2"/>
-      <c r="B40" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="36" t="s">
+        <v>54</v>
+      </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="34" t="str">
-        <f>C10</f>
-        <v>Oswaldo Salmeron Almeida</v>
-      </c>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
-      <c r="B41" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="34" t="str">
-        <f>C12</f>
-        <v>Analista de TI</v>
-      </c>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
@@ -1309,31 +1347,74 @@
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
+      <c r="B43" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="G43" s="34" t="str">
+        <f>C10</f>
+        <v>Oswaldo Salmeron Almeida</v>
+      </c>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="32"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
+      <c r="A44" s="2"/>
+      <c r="B44" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
+      <c r="G44" s="34" t="str">
+        <f>C12</f>
+        <v>Analista de TI</v>
+      </c>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="15">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+    </row>
+    <row r="46" spans="1:10" customHeight="1" ht="15">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="15">
+      <c r="A47" s="32"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1352,23 +1433,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
     <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G44:I44"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1381,7 +1462,16 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H19:I22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H19:I25"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>05/05/2025</t>
+    <t>30/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -98,9 +98,6 @@
     <t>CNK5WW3</t>
   </si>
   <si>
-    <t>Se entrega equipo de computo</t>
-  </si>
-  <si>
     <t>DVZ-VH-TI-00179</t>
   </si>
   <si>
@@ -185,10 +182,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Supervisor TI</t>
+    <t>Darwin Ruiz Aguilar</t>
+  </si>
+  <si>
+    <t>Sala de control</t>
   </si>
 </sst>
 </file>
@@ -1020,9 +1017,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38" t="s">
-        <v>26</v>
-      </c>
+      <c r="H19" s="38"/>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
@@ -1030,7 +1025,7 @@
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
       <c r="D20" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -1043,17 +1038,17 @@
         <v>2</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1064,17 +1059,17 @@
         <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="D22" s="38" t="s">
         <v>32</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>33</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1085,17 +1080,17 @@
         <v>4</v>
       </c>
       <c r="B23" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>35</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>36</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1106,17 +1101,17 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="D24" s="38" t="s">
         <v>39</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>40</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1127,17 +1122,17 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1167,7 +1162,7 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
@@ -1191,7 +1186,7 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
@@ -1204,7 +1199,7 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1217,7 +1212,7 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1230,7 +1225,7 @@
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="24.05">
       <c r="A33" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B33" s="29"/>
       <c r="C33" s="29"/>
@@ -1244,7 +1239,7 @@
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="27">
       <c r="A34" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
@@ -1268,7 +1263,7 @@
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="39">
       <c r="A36" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
@@ -1304,14 +1299,14 @@
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="32"/>
       <c r="B39" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" s="34"/>
       <c r="D39" s="34"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H39" s="35"/>
       <c r="I39" s="35"/>
@@ -1321,7 +1316,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -1354,7 +1349,7 @@
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
       <c r="B43" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
@@ -1370,7 +1365,7 @@
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
       <c r="B44" s="34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C44" s="34"/>
       <c r="D44" s="34"/>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>30/04/2025</t>
+    <t>08/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Tampico</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -101,7 +101,7 @@
     <t>DVZ-VH-TI-00179</t>
   </si>
   <si>
-    <t>Cargador Laptop</t>
+    <t>Cargador de Laptop</t>
   </si>
   <si>
     <t>HA65NS5-00</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Darwin Ruiz Aguilar</t>
-  </si>
-  <si>
-    <t>Sala de control</t>
+    <t>Rednar García Harcía</t>
+  </si>
+  <si>
+    <t>Auxiliar de Supervision</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>08/05/2025</t>
+    <t>13/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Tampico</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Rednar García Harcía</t>
+    <t>Cristobal Soto Escalante</t>
   </si>
   <si>
     <t>Auxiliar de Supervision</t>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>13/05/2025</t>
+    <t>21/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Auxiliar de Supervision</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>21/05/2025</t>
+    <t>09/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -92,6 +92,12 @@
     <t>DELL</t>
   </si>
   <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>1446MG00C698</t>
+  </si>
+  <si>
     <t>Inspiron 15 3000</t>
   </si>
   <si>
@@ -104,16 +110,31 @@
     <t>Cargador de Laptop</t>
   </si>
   <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>K120</t>
+  </si>
+  <si>
+    <t>1446MG0C698O</t>
+  </si>
+  <si>
     <t>HA65NS5-00</t>
   </si>
   <si>
     <t>CN-02D1TJ-CH600-396-00T7-A01</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>Logitech</t>
   </si>
   <si>
     <t>K235</t>
@@ -1021,55 +1042,55 @@
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22" t="s">
+      <c r="A20" s="38">
+        <v>2</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="38">
-        <v>2</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="38" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
       <c r="A22" s="38">
         <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="D22" s="38" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1080,10 +1101,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="38" t="s">
         <v>34</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>31</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>35</v>
@@ -1101,17 +1122,17 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="38" t="s">
         <v>37</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>39</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1122,124 +1143,147 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
+      <c r="A26" s="38">
+        <v>7</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
+      <c r="A27" s="38">
+        <v>8</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
+      <c r="A28" s="38">
+        <v>9</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
+      <c r="A31" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A33" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="27">
+      <c r="A32" s="27"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="15">
+      <c r="A33" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="28" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
@@ -1251,132 +1295,129 @@
       <c r="I34" s="28"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="39">
-      <c r="A36" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
+      <c r="A35" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A36" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="27">
+      <c r="A37" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="2"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="32"/>
-      <c r="B39" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="39">
+      <c r="A39" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="36" t="s">
-        <v>53</v>
-      </c>
+      <c r="A40" s="32"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="G42" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="36" t="s">
+        <v>60</v>
+      </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="34" t="str">
-        <f>C10</f>
-        <v>Oswaldo Salmeron Almeida</v>
-      </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
-      <c r="B44" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="34" t="str">
-        <f>C12</f>
-        <v>Analista de TI</v>
-      </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
@@ -1385,31 +1426,74 @@
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="B46" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="G46" s="34" t="str">
+        <f>C10</f>
+        <v>Oswaldo Salmeron Almeida</v>
+      </c>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
-      <c r="A47" s="32"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
+      <c r="G47" s="34" t="str">
+        <f>C12</f>
+        <v>Analista de TI</v>
+      </c>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+    </row>
+    <row r="48" spans="1:10" customHeight="1" ht="15">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+    </row>
+    <row r="49" spans="1:10" customHeight="1" ht="15">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="1:10" customHeight="1" ht="15">
+      <c r="A50" s="32"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1428,23 +1512,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
     <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="G47:I47"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1466,7 +1550,16 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H19:I25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H19:I28"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="69">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>09/06/2025</t>
+    <t>12/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -119,24 +119,18 @@
     <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
   </si>
   <si>
+    <t>HA65NS5-00</t>
+  </si>
+  <si>
+    <t>CN-02D1TJ-CH600-396-00T7-A01</t>
+  </si>
+  <si>
     <t>Teclado</t>
   </si>
   <si>
     <t>Logitech</t>
   </si>
   <si>
-    <t>K120</t>
-  </si>
-  <si>
-    <t>1446MG0C698O</t>
-  </si>
-  <si>
-    <t>HA65NS5-00</t>
-  </si>
-  <si>
-    <t>CN-02D1TJ-CH600-396-00T7-A01</t>
-  </si>
-  <si>
     <t>K235</t>
   </si>
   <si>
@@ -171,6 +165,30 @@
   </si>
   <si>
     <t>3DX6G04</t>
+  </si>
+  <si>
+    <t>Fijo</t>
+  </si>
+  <si>
+    <t>Kenwood</t>
+  </si>
+  <si>
+    <t>NX-840H-K2</t>
+  </si>
+  <si>
+    <t>B8410042</t>
+  </si>
+  <si>
+    <t>Portátil</t>
+  </si>
+  <si>
+    <t>Hytera</t>
+  </si>
+  <si>
+    <t>PD486</t>
+  </si>
+  <si>
+    <t>23322A0830</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1101,17 +1119,17 @@
         <v>4</v>
       </c>
       <c r="B23" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>33</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>35</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1122,10 +1140,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>37</v>
@@ -1143,17 +1161,17 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1164,17 +1182,17 @@
         <v>7</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1185,17 +1203,17 @@
         <v>8</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1206,84 +1224,92 @@
         <v>9</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
       <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
+      <c r="A29" s="38">
+        <v>10</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
+      <c r="A32" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
+      <c r="A33" s="27"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="28" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
@@ -1296,7 +1322,7 @@
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="28" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
@@ -1307,171 +1333,173 @@
       <c r="H35" s="28"/>
       <c r="I35" s="28"/>
     </row>
-    <row r="36" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A36" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="27">
-      <c r="A37" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="30"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="39">
-      <c r="A39" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-    </row>
-    <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="32"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
+    <row r="36" spans="1:10" customHeight="1" ht="15">
+      <c r="A36" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A37" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="27">
+      <c r="A38" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="15">
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+    </row>
+    <row r="40" spans="1:10" customHeight="1" ht="39">
+      <c r="A40" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="2"/>
+      <c r="A41" s="32"/>
       <c r="B41" s="32"/>
       <c r="C41" s="32"/>
       <c r="D41" s="32"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
+      <c r="G41" s="33"/>
       <c r="H41" s="33"/>
       <c r="I41" s="33"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="32"/>
-      <c r="B42" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="H42" s="35"/>
-      <c r="I42" s="35"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="36" t="s">
-        <v>60</v>
-      </c>
+      <c r="A43" s="32"/>
+      <c r="B43" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="G43" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="36" t="s">
+        <v>66</v>
+      </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="2"/>
-      <c r="B46" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="34" t="str">
-        <f>C10</f>
-        <v>Oswaldo Salmeron Almeida</v>
-      </c>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="2"/>
       <c r="B47" s="34" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C47" s="34"/>
       <c r="D47" s="34"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="34" t="str">
+        <f>C10</f>
+        <v>Oswaldo Salmeron Almeida</v>
+      </c>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+    </row>
+    <row r="48" spans="1:10" customHeight="1" ht="15">
+      <c r="A48" s="2"/>
+      <c r="B48" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="34" t="str">
         <f>C12</f>
         <v>Analista de TI</v>
       </c>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-    </row>
-    <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="2"/>
@@ -1480,20 +1508,31 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
-      <c r="A50" s="32"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:10" customHeight="1" ht="15">
+      <c r="A51" s="32"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1512,23 +1551,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A39:I39"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="G43:I43"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="G47:I47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="G48:I48"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1559,7 +1598,10 @@
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H19:I28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H19:I29"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="71">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -119,18 +119,24 @@
     <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
   </si>
   <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>K120</t>
+  </si>
+  <si>
+    <t>1446MG0C698O</t>
+  </si>
+  <si>
     <t>HA65NS5-00</t>
   </si>
   <si>
     <t>CN-02D1TJ-CH600-396-00T7-A01</t>
   </si>
   <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
     <t>K235</t>
   </si>
   <si>
@@ -221,10 +227,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
+    <t>Cristobal Soto Escalante</t>
+  </si>
+  <si>
+    <t>Coordinador de Proyectos</t>
   </si>
 </sst>
 </file>
@@ -1119,17 +1125,17 @@
         <v>4</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1140,10 +1146,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>37</v>
@@ -1161,17 +1167,17 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="38" t="s">
         <v>39</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>40</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1182,17 +1188,17 @@
         <v>7</v>
       </c>
       <c r="B26" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="38" t="s">
         <v>42</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>44</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1203,17 +1209,17 @@
         <v>8</v>
       </c>
       <c r="B27" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="38" t="s">
         <v>46</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>47</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1224,17 +1230,17 @@
         <v>9</v>
       </c>
       <c r="B28" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="38" t="s">
         <v>49</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>51</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1245,84 +1251,92 @@
         <v>10</v>
       </c>
       <c r="B29" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="38" t="s">
         <v>53</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>55</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
+      <c r="A30" s="38">
+        <v>11</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
+      <c r="A33" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
+      <c r="A34" s="27"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
@@ -1335,7 +1349,7 @@
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
@@ -1346,171 +1360,173 @@
       <c r="H36" s="28"/>
       <c r="I36" s="28"/>
     </row>
-    <row r="37" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A37" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="27">
-      <c r="A38" s="28" t="s">
+    <row r="37" spans="1:10" customHeight="1" ht="15">
+      <c r="A37" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="30"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-    </row>
-    <row r="40" spans="1:10" customHeight="1" ht="39">
-      <c r="A40" s="31" t="s">
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A38" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-    </row>
-    <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="32"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="27">
+      <c r="A39" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+    </row>
+    <row r="40" spans="1:10" customHeight="1" ht="15">
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+    </row>
+    <row r="41" spans="1:10" customHeight="1" ht="39">
+      <c r="A41" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="2"/>
+      <c r="A42" s="32"/>
       <c r="B42" s="32"/>
       <c r="C42" s="32"/>
       <c r="D42" s="32"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
+      <c r="G42" s="33"/>
       <c r="H42" s="33"/>
       <c r="I42" s="33"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
-      <c r="A43" s="32"/>
-      <c r="B43" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="36" t="s">
+      <c r="A44" s="32"/>
+      <c r="B44" s="34" t="s">
         <v>66</v>
       </c>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
+      <c r="G44" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="36" t="s">
+        <v>68</v>
+      </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="37"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="2"/>
-      <c r="B47" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="34" t="str">
-        <f>C10</f>
-        <v>Oswaldo Salmeron Almeida</v>
-      </c>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
       <c r="A48" s="2"/>
       <c r="B48" s="34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C48" s="34"/>
       <c r="D48" s="34"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="34" t="str">
+        <f>C10</f>
+        <v>Oswaldo Salmeron Almeida</v>
+      </c>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+    </row>
+    <row r="49" spans="1:10" customHeight="1" ht="15">
+      <c r="A49" s="2"/>
+      <c r="B49" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="34" t="str">
         <f>C12</f>
         <v>Analista de TI</v>
       </c>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
-    </row>
-    <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="2"/>
@@ -1519,20 +1535,31 @@
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
-      <c r="A51" s="32"/>
-      <c r="B51" s="32"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:10" customHeight="1" ht="15">
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1551,23 +1578,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A39:I39"/>
     <mergeCell ref="A40:I40"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G44:I44"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="G48:I48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="G49:I49"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1601,7 +1628,10 @@
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H19:I29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H19:I30"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>12/06/2025</t>
+    <t>16/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Coordinador de Proyectos</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,172 +41,148 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>25/06/2025</t>
+    <t>08/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>Región:</t>
+  </si>
+  <si>
+    <t>Sur</t>
+  </si>
+  <si>
+    <t>Ubicación:</t>
+  </si>
+  <si>
+    <t>Base Operativa</t>
+  </si>
+  <si>
+    <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>MARCA</t>
+  </si>
+  <si>
+    <t>MODELO</t>
+  </si>
+  <si>
+    <t>NUMERO DE SERIE</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Inspiron 15 3000</t>
+  </si>
+  <si>
+    <t>CNK5WW3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00179</t>
+  </si>
+  <si>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>HA65NS5-00</t>
+  </si>
+  <si>
+    <t>CN-02D1TJ-CH600-396-00T7-A01</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>K235</t>
+  </si>
+  <si>
+    <t>2212MR022038</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>M170</t>
+  </si>
+  <si>
+    <t>2207LZX03WG8</t>
+  </si>
+  <si>
+    <t>Adaptador Tipo C</t>
+  </si>
+  <si>
+    <t>Avedistante</t>
+  </si>
+  <si>
+    <t>BL10V</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>E2724HS</t>
+  </si>
+  <si>
+    <t>3DX6G04</t>
+  </si>
+  <si>
+    <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
+  </si>
+  <si>
+    <t>1. El uso correcto del equipo asignado.</t>
+  </si>
+  <si>
+    <t>2. Permitir realizar la auditoría y mantenimiento programado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Reportar cualquier anomalía al área de TI. </t>
+  </si>
+  <si>
+    <t>4. Hago constar que el equipo de cómputo es intransferible y esta estríctamente prohibido dejarlo en lugares de exposición de riesgo, daño y/o extravío.</t>
+  </si>
+  <si>
+    <t>5. Comunicar en caso de robo o extravío al área de TI.</t>
+  </si>
+  <si>
+    <t>Acepto que he comprendido claramente las responsabilidades que tengo con los equipos de trabajo que la empresa me ha otorgado y que el uso es exclusivamente laboral.</t>
+  </si>
+  <si>
+    <t>ENTREGA:</t>
+  </si>
+  <si>
+    <t>ACEPTA Y RECIBE:</t>
+  </si>
+  <si>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
+  </si>
+  <si>
     <t>Analista de TI</t>
-  </si>
-  <si>
-    <t>Región:</t>
-  </si>
-  <si>
-    <t>Sur</t>
-  </si>
-  <si>
-    <t>Ubicación:</t>
-  </si>
-  <si>
-    <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>TIPO</t>
-  </si>
-  <si>
-    <t>MARCA</t>
-  </si>
-  <si>
-    <t>MODELO</t>
-  </si>
-  <si>
-    <t>NUMERO DE SERIE</t>
-  </si>
-  <si>
-    <t>OBSERVACIONES</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>Inspiron 15 3000</t>
-  </si>
-  <si>
-    <t>CNK5WW3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00179</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>K120</t>
-  </si>
-  <si>
-    <t>1446MG0C698O</t>
-  </si>
-  <si>
-    <t>Cargador de Laptop</t>
-  </si>
-  <si>
-    <t>HA65NS5-00</t>
-  </si>
-  <si>
-    <t>CN-02D1TJ-CH600-396-00T7-A01</t>
-  </si>
-  <si>
-    <t>K235</t>
-  </si>
-  <si>
-    <t>2212MR022038</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>M170</t>
-  </si>
-  <si>
-    <t>2207LZX03WG8</t>
-  </si>
-  <si>
-    <t>Adaptador Tipo C</t>
-  </si>
-  <si>
-    <t>Avedistante</t>
-  </si>
-  <si>
-    <t>BL10V</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>E2724HS</t>
-  </si>
-  <si>
-    <t>3DX6G04</t>
-  </si>
-  <si>
-    <t>Fijo</t>
-  </si>
-  <si>
-    <t>Kenwood</t>
-  </si>
-  <si>
-    <t>NX-840H-K2</t>
-  </si>
-  <si>
-    <t>B8410042</t>
-  </si>
-  <si>
-    <t>Portátil</t>
-  </si>
-  <si>
-    <t>Hytera</t>
-  </si>
-  <si>
-    <t>PD486</t>
-  </si>
-  <si>
-    <t>23322A0830</t>
-  </si>
-  <si>
-    <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
-  </si>
-  <si>
-    <t>1. El uso correcto del equipo asignado.</t>
-  </si>
-  <si>
-    <t>2. Permitir realizar la auditoría y mantenimiento programado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Reportar cualquier anomalía al área de TI. </t>
-  </si>
-  <si>
-    <t>4. Hago constar que el equipo de cómputo es intransferible y esta estríctamente prohibido dejarlo en lugares de exposición de riesgo, daño y/o extravío.</t>
-  </si>
-  <si>
-    <t>5. Comunicar en caso de robo o extravío al área de TI.</t>
-  </si>
-  <si>
-    <t>Acepto que he comprendido claramente las responsabilidades que tengo con los equipos de trabajo que la empresa me ha otorgado y que el uso es exclusivamente laboral.</t>
-  </si>
-  <si>
-    <t>ENTREGA:</t>
-  </si>
-  <si>
-    <t>ACEPTA Y RECIBE:</t>
-  </si>
-  <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -354,6 +330,32 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -422,32 +424,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -536,59 +512,59 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
@@ -873,7 +849,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -890,73 +866,73 @@
     <row r="1" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="2" spans="1:11" customHeight="1" ht="15.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="27" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="33" t="s">
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="34"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="3" spans="1:11" customHeight="1" ht="15.75">
       <c r="A3" s="1"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="33" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="4" spans="1:11" customHeight="1" ht="15.75">
       <c r="A4" s="1"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="33" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="34"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" customHeight="1" ht="15.75">
       <c r="A5" s="1"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="27" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="35"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="49"/>
     </row>
     <row r="6" spans="1:11" customHeight="1" ht="9.75">
       <c r="A6" s="1"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="36"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="50"/>
     </row>
     <row r="7" spans="1:11" customHeight="1" ht="15.75">
       <c r="H7" s="2"/>
@@ -968,14 +944,14 @@
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1011,7 +987,9 @@
       <c r="I10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="6"/>
+      <c r="J10" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
       <c r="G11" s="12"/>
@@ -1019,40 +997,40 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+        <v>15</v>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
     </row>
     <row r="13" spans="1:11" customHeight="1" ht="15.75">
       <c r="A13" s="13"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
     </row>
     <row r="14" spans="1:11" customHeight="1" ht="15.75">
       <c r="A14" s="13"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
     </row>
     <row r="15" spans="1:11" customHeight="1" ht="15.75">
       <c r="A15" s="14"/>
@@ -1068,26 +1046,26 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="34"/>
+        <v>19</v>
+      </c>
+      <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="34"/>
+        <v>20</v>
+      </c>
+      <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="34"/>
+        <v>21</v>
+      </c>
+      <c r="J16" s="40"/>
       <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:11">
@@ -1096,17 +1074,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" s="53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1119,7 +1097,7 @@
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1134,10 +1112,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E19" s="53" t="s">
         <v>28</v>
@@ -1160,14 +1138,14 @@
         <v>30</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
@@ -1180,17 +1158,17 @@
         <v>4</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1203,17 +1181,17 @@
         <v>5</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
@@ -1226,363 +1204,293 @@
         <v>6</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
       <c r="J23" s="53"/>
       <c r="K23" s="17"/>
     </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="52"/>
-      <c r="B24" s="53">
-        <v>7</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53" t="s">
+    <row r="24" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A24" s="18"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="31"/>
+    </row>
+    <row r="25" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A25" s="18"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="31"/>
+    </row>
+    <row r="26" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A27" s="19"/>
+      <c r="B27" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="17"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="52"/>
-      <c r="B25" s="53">
-        <v>8</v>
-      </c>
-      <c r="C25" s="53" t="s">
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+    </row>
+    <row r="28" spans="1:11" customHeight="1" ht="9">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A29" s="20"/>
+      <c r="B29" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+    </row>
+    <row r="30" spans="1:11" customHeight="1" ht="15">
+      <c r="A30" s="20"/>
+      <c r="B30" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="53" t="s">
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+    </row>
+    <row r="31" spans="1:11" customHeight="1" ht="15">
+      <c r="A31" s="20"/>
+      <c r="B31" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53" t="s">
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+    </row>
+    <row r="32" spans="1:11" customHeight="1" ht="15">
+      <c r="A32" s="20"/>
+      <c r="B32" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="17"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="52"/>
-      <c r="B26" s="53">
-        <v>9</v>
-      </c>
-      <c r="C26" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="17"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A27" s="18"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="48"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A28" s="18"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="48"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A30" s="19"/>
-      <c r="B30" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="9">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A32" s="20"/>
-      <c r="B32" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
     </row>
     <row r="33" spans="1:11" customHeight="1" ht="15">
       <c r="A33" s="20"/>
-      <c r="B33" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-    </row>
-    <row r="34" spans="1:11" customHeight="1" ht="15">
-      <c r="A34" s="20"/>
-      <c r="B34" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-    </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15">
-      <c r="A35" s="20"/>
-      <c r="B35" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-    </row>
-    <row r="36" spans="1:11" customHeight="1" ht="15">
-      <c r="A36" s="20"/>
-      <c r="B36" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-    </row>
-    <row r="37" spans="1:11" customHeight="1" ht="12">
-      <c r="A37" s="21"/>
-      <c r="B37" s="44"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A38" s="17"/>
-      <c r="B38" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-    </row>
-    <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-    </row>
+      <c r="B33" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+    </row>
+    <row r="34" spans="1:11" customHeight="1" ht="12">
+      <c r="A34" s="21"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+    </row>
+    <row r="35" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A35" s="17"/>
+      <c r="B35" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+    </row>
+    <row r="36" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+    </row>
+    <row r="37" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+    </row>
+    <row r="38" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="H38" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+    </row>
+    <row r="39" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="H41" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
-    </row>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-    </row>
-    <row r="44" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="45" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C45" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="H45" s="41" t="str">
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+    </row>
+    <row r="41" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="42" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C42" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="H42" s="25" t="str">
         <f>C8</f>
         <v>Oswaldo Salmeron Almeida</v>
       </c>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-    </row>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+    </row>
+    <row r="43" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C43" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="H43" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+    </row>
+    <row r="44" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+    </row>
+    <row r="45" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="46" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C46" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="H46" s="41" t="str">
-        <f>C10</f>
-        <v>Analista de TI</v>
-      </c>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-    </row>
-    <row r="47" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-    </row>
-    <row r="48" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="49" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="B38:J38"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="B12:J14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="C2:H4"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="C5:J6"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="B12:J14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B35:J35"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1604,16 +1512,7 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="I23:J23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I17:J26"/>
+    <mergeCell ref="I17:J23"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Área:</t>
   </si>
   <si>
-    <t>TI</t>
+    <t>po</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>Base Operativa</t>
+    <t>et</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -83,70 +83,16 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>Inspiron 15 3000</t>
-  </si>
-  <si>
-    <t>CNK5WW3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00179</t>
-  </si>
-  <si>
-    <t>Cargador de Laptop</t>
-  </si>
-  <si>
-    <t>HA65NS5-00</t>
-  </si>
-  <si>
-    <t>CN-02D1TJ-CH600-396-00T7-A01</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>K235</t>
-  </si>
-  <si>
-    <t>2212MR022038</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>M170</t>
-  </si>
-  <si>
-    <t>2207LZX03WG8</t>
-  </si>
-  <si>
-    <t>Adaptador Tipo C</t>
-  </si>
-  <si>
-    <t>Avedistante</t>
-  </si>
-  <si>
-    <t>BL10V</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>E2724HS</t>
-  </si>
-  <si>
-    <t>3DX6G04</t>
+    <t>Teléfono Celular</t>
+  </si>
+  <si>
+    <t>Lg</t>
+  </si>
+  <si>
+    <t>LG00000000001</t>
+  </si>
+  <si>
+    <t>Linea: 9988778899</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -455,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -573,6 +519,9 @@
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -849,7 +798,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1083,184 +1032,138 @@
         <v>24</v>
       </c>
       <c r="F17" s="53"/>
-      <c r="G17" s="53" t="s">
-        <v>25</v>
+      <c r="G17" s="53">
+        <v>89762879520</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="52"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="51" t="s">
+    <row r="18" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A18" s="18"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="31"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="31"/>
+    </row>
+    <row r="19" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A19" s="18"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="31"/>
+    </row>
+    <row r="20" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A21" s="19"/>
+      <c r="B21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="17"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="52"/>
-      <c r="B19" s="53">
-        <v>2</v>
-      </c>
-      <c r="C19" s="53" t="s">
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+    </row>
+    <row r="22" spans="1:11" customHeight="1" ht="9">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A23" s="20"/>
+      <c r="B23" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="53" t="s">
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+    </row>
+    <row r="24" spans="1:11" customHeight="1" ht="15">
+      <c r="A24" s="20"/>
+      <c r="B24" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53" t="s">
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+    </row>
+    <row r="25" spans="1:11" customHeight="1" ht="15">
+      <c r="A25" s="20"/>
+      <c r="B25" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="17"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="52"/>
-      <c r="B20" s="53">
-        <v>3</v>
-      </c>
-      <c r="C20" s="53" t="s">
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+    </row>
+    <row r="26" spans="1:11" customHeight="1" ht="15">
+      <c r="A26" s="20"/>
+      <c r="B26" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+    </row>
+    <row r="27" spans="1:11" customHeight="1" ht="15">
+      <c r="A27" s="20"/>
+      <c r="B27" s="27" t="s">
         <v>31</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="17"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="52"/>
-      <c r="B21" s="53">
-        <v>4</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="52"/>
-      <c r="B22" s="53">
-        <v>5</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="17"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="52"/>
-      <c r="B23" s="53">
-        <v>6</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="17"/>
-    </row>
-    <row r="24" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A24" s="18"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="31"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A25" s="18"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="31"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A27" s="19"/>
-      <c r="B27" s="33" t="s">
-        <v>44</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
@@ -1271,22 +1174,22 @@
       <c r="I27" s="26"/>
       <c r="J27" s="26"/>
     </row>
-    <row r="28" spans="1:11" customHeight="1" ht="9">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A29" s="20"/>
-      <c r="B29" s="27" t="s">
-        <v>45</v>
+    <row r="28" spans="1:11" customHeight="1" ht="12">
+      <c r="A28" s="21"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+    </row>
+    <row r="29" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A29" s="17"/>
+      <c r="B29" s="29" t="s">
+        <v>32</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -1297,166 +1200,84 @@
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
     </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15">
-      <c r="A30" s="20"/>
-      <c r="B30" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15">
-      <c r="A31" s="20"/>
-      <c r="B31" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15">
-      <c r="A32" s="20"/>
-      <c r="B32" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="26"/>
+    <row r="30" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="25" t="s">
+        <v>33</v>
+      </c>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
+      <c r="H32" s="34" t="s">
+        <v>34</v>
+      </c>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
     </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15">
-      <c r="A33" s="20"/>
-      <c r="B33" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-    </row>
-    <row r="34" spans="1:11" customHeight="1" ht="12">
-      <c r="A34" s="21"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-    </row>
-    <row r="35" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A35" s="17"/>
-      <c r="B35" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-    </row>
+    <row r="33" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="34" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+    </row>
+    <row r="35" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="36" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
+      <c r="C36" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="H36" s="25" t="str">
+        <f>C8</f>
+        <v>Oswaldo Salmeron Almeida</v>
+      </c>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
     </row>
     <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
+      <c r="C37" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="H37" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
     </row>
     <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="H38" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
     </row>
     <row r="39" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-    </row>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C42" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="H42" s="25" t="str">
-        <f>C8</f>
-        <v>Oswaldo Salmeron Almeida</v>
-      </c>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-    </row>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C43" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="H43" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-    </row>
-    <row r="44" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-    </row>
-    <row r="45" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="46" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1471,48 +1292,29 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I17:J23"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>08/07/2025</t>
+    <t>09/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>po</t>
+    <t>TI</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>et</t>
+    <t>TII</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>

--- a/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
+++ b/database/controller_excel/Resguardo_Oswaldo_Salmeron_Almeida.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="37">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>09/07/2025</t>
+    <t>15/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>TI</t>
+    <t>ds</t>
   </si>
   <si>
     <t>Región:</t>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>Ubicación:</t>
-  </si>
-  <si>
-    <t>TII</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -937,7 +934,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -946,7 +943,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -995,24 +992,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1023,13 +1020,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="E17" s="53" t="s">
         <v>23</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53">
@@ -1046,7 +1043,7 @@
       <c r="C18" s="24"/>
       <c r="D18" s="24"/>
       <c r="E18" s="54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="31"/>
       <c r="G18" s="35"/>
@@ -1081,7 +1078,7 @@
     <row r="21" spans="1:11" customHeight="1" ht="15.75">
       <c r="A21" s="19"/>
       <c r="B21" s="33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="26"/>
@@ -1107,7 +1104,7 @@
     <row r="23" spans="1:11" customHeight="1" ht="15.75">
       <c r="A23" s="20"/>
       <c r="B23" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="26"/>
       <c r="D23" s="26"/>
@@ -1121,7 +1118,7 @@
     <row r="24" spans="1:11" customHeight="1" ht="15">
       <c r="A24" s="20"/>
       <c r="B24" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26"/>
@@ -1135,7 +1132,7 @@
     <row r="25" spans="1:11" customHeight="1" ht="15">
       <c r="A25" s="20"/>
       <c r="B25" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
@@ -1149,7 +1146,7 @@
     <row r="26" spans="1:11" customHeight="1" ht="15">
       <c r="A26" s="20"/>
       <c r="B26" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
@@ -1163,7 +1160,7 @@
     <row r="27" spans="1:11" customHeight="1" ht="15">
       <c r="A27" s="20"/>
       <c r="B27" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
@@ -1189,7 +1186,7 @@
     <row r="29" spans="1:11" customHeight="1" ht="27.75">
       <c r="A29" s="17"/>
       <c r="B29" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -1221,12 +1218,12 @@
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
       <c r="H32" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
@@ -1243,7 +1240,7 @@
     <row r="35" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="36" spans="1:11" customHeight="1" ht="15.75">
       <c r="C36" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
@@ -1256,12 +1253,12 @@
     </row>
     <row r="37" spans="1:11" customHeight="1" ht="15.75">
       <c r="C37" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
       <c r="H37" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I37" s="26"/>
       <c r="J37" s="26"/>
